--- a/Basic/data/PCR.xlsx
+++ b/Basic/data/PCR.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubarcelona.sharepoint.com/sites/extub/gre/autoim/Documents compartits/Investigadors d'AiT/06 Projectes/25 PREV-AL-DI/2 Tesis Elsa/R/R basics/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubarcelona.sharepoint.com/sites/extub/gre/autoim/Documents compartits/Investigadors d'AiT/06 Projectes/25 PREV-AL-DI/2 Tesis Elsa/R/R basics/Basic/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{E71F6D1D-06DC-41AE-AFA5-7AB09D718BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4612DC59-2D05-4D66-8291-BB3B8D90428B}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{E71F6D1D-06DC-41AE-AFA5-7AB09D718BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5AFBAD9-BDE1-4469-B67E-D7372BF29184}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1008" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="relative" sheetId="1" r:id="rId1"/>
+    <sheet name="for_correlation" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="156">
   <si>
     <t>CA</t>
   </si>
@@ -453,6 +454,54 @@
   </si>
   <si>
     <t>T7.2</t>
+  </si>
+  <si>
+    <t>gene_1_M</t>
+  </si>
+  <si>
+    <t>gene_2_M</t>
+  </si>
+  <si>
+    <t>gene_3_M</t>
+  </si>
+  <si>
+    <t>gene_4_M</t>
+  </si>
+  <si>
+    <t>gene_1_Cd21</t>
+  </si>
+  <si>
+    <t>gene_2_Cd21</t>
+  </si>
+  <si>
+    <t>gene_3_Cd21</t>
+  </si>
+  <si>
+    <t>gene_4_Cd21</t>
+  </si>
+  <si>
+    <t>gene_1_Cd1</t>
+  </si>
+  <si>
+    <t>gene_2_Cd1</t>
+  </si>
+  <si>
+    <t>gene_3_Cd1</t>
+  </si>
+  <si>
+    <t>gene_4_Cd1</t>
+  </si>
+  <si>
+    <t>gene_1_CA</t>
+  </si>
+  <si>
+    <t>gene_2_CA</t>
+  </si>
+  <si>
+    <t>gene_3_CA</t>
+  </si>
+  <si>
+    <t>gene_4_CA</t>
   </si>
 </sst>
 </file>
@@ -4335,7 +4384,1291 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{277444DC-AE29-45CA-A84D-D9FD47AF2214}">
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>105</v>
+      </c>
+      <c r="C2">
+        <v>94</v>
+      </c>
+      <c r="D2">
+        <v>95.199999999999989</v>
+      </c>
+      <c r="E2">
+        <v>101</v>
+      </c>
+      <c r="F2">
+        <v>84.5</v>
+      </c>
+      <c r="G2">
+        <v>105.69999999999999</v>
+      </c>
+      <c r="H2">
+        <v>97.899999999999991</v>
+      </c>
+      <c r="I2">
+        <v>100.2</v>
+      </c>
+      <c r="J2">
+        <v>99.4</v>
+      </c>
+      <c r="K2">
+        <v>100.89999999999999</v>
+      </c>
+      <c r="L2">
+        <v>118.5</v>
+      </c>
+      <c r="M2">
+        <v>90.8</v>
+      </c>
+      <c r="N2">
+        <v>93.8</v>
+      </c>
+      <c r="O2">
+        <v>108.2</v>
+      </c>
+      <c r="P2">
+        <v>94.399999999999991</v>
+      </c>
+      <c r="Q2">
+        <v>101.29999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>98.6</v>
+      </c>
+      <c r="C3">
+        <v>118.5</v>
+      </c>
+      <c r="D3">
+        <v>98.1</v>
+      </c>
+      <c r="E3">
+        <v>109.7</v>
+      </c>
+      <c r="F3">
+        <v>100.69999999999999</v>
+      </c>
+      <c r="G3">
+        <v>111.4</v>
+      </c>
+      <c r="H3">
+        <v>95.1</v>
+      </c>
+      <c r="I3">
+        <v>105</v>
+      </c>
+      <c r="J3">
+        <v>109.60000000000001</v>
+      </c>
+      <c r="K3">
+        <v>98.4</v>
+      </c>
+      <c r="L3">
+        <v>111.3</v>
+      </c>
+      <c r="M3">
+        <v>86.5</v>
+      </c>
+      <c r="N3">
+        <v>94.399999999999991</v>
+      </c>
+      <c r="O3">
+        <v>105.1</v>
+      </c>
+      <c r="P3">
+        <v>118.8</v>
+      </c>
+      <c r="Q3">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>106.5</v>
+      </c>
+      <c r="C4">
+        <v>99.9</v>
+      </c>
+      <c r="D4">
+        <v>88.9</v>
+      </c>
+      <c r="F4">
+        <v>89.4</v>
+      </c>
+      <c r="H4">
+        <v>94.1</v>
+      </c>
+      <c r="J4">
+        <v>90.100000000000009</v>
+      </c>
+      <c r="K4">
+        <v>111.7</v>
+      </c>
+      <c r="L4">
+        <v>97.3</v>
+      </c>
+      <c r="M4">
+        <v>90.2</v>
+      </c>
+      <c r="N4">
+        <v>93.600000000000009</v>
+      </c>
+      <c r="P4">
+        <v>85.5</v>
+      </c>
+      <c r="Q4">
+        <v>108.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5">
+        <v>115.19999999999999</v>
+      </c>
+      <c r="C5">
+        <v>89.4</v>
+      </c>
+      <c r="D5">
+        <v>88</v>
+      </c>
+      <c r="E5">
+        <v>96.7</v>
+      </c>
+      <c r="F5">
+        <v>104.69999999999999</v>
+      </c>
+      <c r="G5">
+        <v>106.5</v>
+      </c>
+      <c r="H5">
+        <v>108.5</v>
+      </c>
+      <c r="I5">
+        <v>109.60000000000001</v>
+      </c>
+      <c r="J5">
+        <v>105</v>
+      </c>
+      <c r="K5">
+        <v>102.49999999999999</v>
+      </c>
+      <c r="L5">
+        <v>88.9</v>
+      </c>
+      <c r="M5">
+        <v>110.5</v>
+      </c>
+      <c r="N5">
+        <v>111.9</v>
+      </c>
+      <c r="O5">
+        <v>111.7</v>
+      </c>
+      <c r="P5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
+        <v>97.7</v>
+      </c>
+      <c r="C6">
+        <v>108.2</v>
+      </c>
+      <c r="D6">
+        <v>108.1</v>
+      </c>
+      <c r="E6">
+        <v>96.1</v>
+      </c>
+      <c r="F6">
+        <v>90.8</v>
+      </c>
+      <c r="G6">
+        <v>96.8</v>
+      </c>
+      <c r="H6">
+        <v>103.60000000000001</v>
+      </c>
+      <c r="I6">
+        <v>121.50000000000001</v>
+      </c>
+      <c r="J6">
+        <v>94.699999999999989</v>
+      </c>
+      <c r="K6">
+        <v>103.4</v>
+      </c>
+      <c r="L6">
+        <v>125.69999999999999</v>
+      </c>
+      <c r="M6">
+        <v>90.5</v>
+      </c>
+      <c r="N6">
+        <v>114.19999999999999</v>
+      </c>
+      <c r="O6">
+        <v>113.79999999999998</v>
+      </c>
+      <c r="P6">
+        <v>104.4</v>
+      </c>
+      <c r="Q6">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>97.7</v>
+      </c>
+      <c r="C7">
+        <v>87.8</v>
+      </c>
+      <c r="E7">
+        <v>85.399999999999991</v>
+      </c>
+      <c r="F7">
+        <v>121.9</v>
+      </c>
+      <c r="G7">
+        <v>90.600000000000009</v>
+      </c>
+      <c r="H7">
+        <v>80.5</v>
+      </c>
+      <c r="I7">
+        <v>96</v>
+      </c>
+      <c r="J7">
+        <v>106.69999999999999</v>
+      </c>
+      <c r="K7">
+        <v>92</v>
+      </c>
+      <c r="L7">
+        <v>97.3</v>
+      </c>
+      <c r="M7">
+        <v>92.7</v>
+      </c>
+      <c r="O7">
+        <v>118.5</v>
+      </c>
+      <c r="P7">
+        <v>84.8</v>
+      </c>
+      <c r="Q7">
+        <v>114.39999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>133.1</v>
+      </c>
+      <c r="D8">
+        <v>128.9</v>
+      </c>
+      <c r="E8">
+        <v>134.4</v>
+      </c>
+      <c r="F8">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="G8">
+        <v>119</v>
+      </c>
+      <c r="I8">
+        <v>116.5</v>
+      </c>
+      <c r="J8">
+        <v>125.89999999999999</v>
+      </c>
+      <c r="K8">
+        <v>130.29999999999998</v>
+      </c>
+      <c r="L8">
+        <v>148.70000000000002</v>
+      </c>
+      <c r="M8">
+        <v>140.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>141.5</v>
+      </c>
+      <c r="C9">
+        <v>100.6</v>
+      </c>
+      <c r="D9">
+        <v>145.1</v>
+      </c>
+      <c r="E9">
+        <v>133.9</v>
+      </c>
+      <c r="F9">
+        <v>135.20000000000002</v>
+      </c>
+      <c r="G9">
+        <v>133.20000000000002</v>
+      </c>
+      <c r="H9">
+        <v>146.5</v>
+      </c>
+      <c r="I9">
+        <v>137.4</v>
+      </c>
+      <c r="J9">
+        <v>95.5</v>
+      </c>
+      <c r="K9">
+        <v>155.1</v>
+      </c>
+      <c r="L9">
+        <v>98.9</v>
+      </c>
+      <c r="M9">
+        <v>121.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
+        <v>123</v>
+      </c>
+      <c r="D10">
+        <v>135.4</v>
+      </c>
+      <c r="E10">
+        <v>130.1</v>
+      </c>
+      <c r="G10">
+        <v>130.69999999999999</v>
+      </c>
+      <c r="H10">
+        <v>142.4</v>
+      </c>
+      <c r="I10">
+        <v>110.2</v>
+      </c>
+      <c r="J10">
+        <v>107.3</v>
+      </c>
+      <c r="K10">
+        <v>134.9</v>
+      </c>
+      <c r="L10">
+        <v>124.9</v>
+      </c>
+      <c r="M10">
+        <v>139.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11">
+        <v>138.1</v>
+      </c>
+      <c r="C11">
+        <v>133</v>
+      </c>
+      <c r="D11">
+        <v>120.30000000000001</v>
+      </c>
+      <c r="E11">
+        <v>126.49999999999999</v>
+      </c>
+      <c r="F11">
+        <v>133.5</v>
+      </c>
+      <c r="G11">
+        <v>120.19999999999999</v>
+      </c>
+      <c r="H11">
+        <v>142.19999999999999</v>
+      </c>
+      <c r="I11">
+        <v>157.5</v>
+      </c>
+      <c r="J11">
+        <v>150.5</v>
+      </c>
+      <c r="K11">
+        <v>126.69999999999999</v>
+      </c>
+      <c r="M11">
+        <v>144.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12">
+        <v>123</v>
+      </c>
+      <c r="C12">
+        <v>141.1</v>
+      </c>
+      <c r="D12">
+        <v>135.4</v>
+      </c>
+      <c r="E12">
+        <v>108.80000000000001</v>
+      </c>
+      <c r="F12">
+        <v>134.4</v>
+      </c>
+      <c r="G12">
+        <v>162.20000000000002</v>
+      </c>
+      <c r="H12">
+        <v>149.6</v>
+      </c>
+      <c r="K12">
+        <v>142.4</v>
+      </c>
+      <c r="L12">
+        <v>108.89999999999999</v>
+      </c>
+      <c r="M12">
+        <v>139.30000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13">
+        <v>123</v>
+      </c>
+      <c r="C13">
+        <v>132.6</v>
+      </c>
+      <c r="D13">
+        <v>153.1</v>
+      </c>
+      <c r="E13">
+        <v>123.70000000000002</v>
+      </c>
+      <c r="F13">
+        <v>141.70000000000002</v>
+      </c>
+      <c r="G13">
+        <v>146.30000000000001</v>
+      </c>
+      <c r="H13">
+        <v>131.80000000000001</v>
+      </c>
+      <c r="I13">
+        <v>132.29999999999998</v>
+      </c>
+      <c r="J13">
+        <v>126.69999999999999</v>
+      </c>
+      <c r="K13">
+        <v>123.9</v>
+      </c>
+      <c r="L13">
+        <v>131.6</v>
+      </c>
+      <c r="M13">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>93.600000000000009</v>
+      </c>
+      <c r="C14">
+        <v>88.3</v>
+      </c>
+      <c r="D14">
+        <v>89.5</v>
+      </c>
+      <c r="F14">
+        <v>76.7</v>
+      </c>
+      <c r="G14">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="H14">
+        <v>89.8</v>
+      </c>
+      <c r="I14">
+        <v>100.69999999999999</v>
+      </c>
+      <c r="J14">
+        <v>89.9</v>
+      </c>
+      <c r="K14">
+        <v>91.100000000000009</v>
+      </c>
+      <c r="L14">
+        <v>84.6</v>
+      </c>
+      <c r="M14">
+        <v>96.399999999999991</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>61.3</v>
+      </c>
+      <c r="D15">
+        <v>113.5</v>
+      </c>
+      <c r="E15">
+        <v>78</v>
+      </c>
+      <c r="F15">
+        <v>77.8</v>
+      </c>
+      <c r="H15">
+        <v>76.5</v>
+      </c>
+      <c r="I15">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="J15">
+        <v>112.20000000000002</v>
+      </c>
+      <c r="K15">
+        <v>82.8</v>
+      </c>
+      <c r="L15">
+        <v>107.4</v>
+      </c>
+      <c r="M15">
+        <v>93.100000000000009</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="C16">
+        <v>67.800000000000011</v>
+      </c>
+      <c r="D16">
+        <v>50.7</v>
+      </c>
+      <c r="E16">
+        <v>87.6</v>
+      </c>
+      <c r="F16">
+        <v>88.8</v>
+      </c>
+      <c r="G16">
+        <v>121.8</v>
+      </c>
+      <c r="H16">
+        <v>91.100000000000009</v>
+      </c>
+      <c r="I16">
+        <v>67</v>
+      </c>
+      <c r="J16">
+        <v>91.2</v>
+      </c>
+      <c r="K16">
+        <v>97.2</v>
+      </c>
+      <c r="L16">
+        <v>73.8</v>
+      </c>
+      <c r="M16">
+        <v>94.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="C17">
+        <v>79.2</v>
+      </c>
+      <c r="D17">
+        <v>102.3</v>
+      </c>
+      <c r="E17">
+        <v>96.1</v>
+      </c>
+      <c r="F17">
+        <v>95.1</v>
+      </c>
+      <c r="G17">
+        <v>105.5</v>
+      </c>
+      <c r="H17">
+        <v>79.800000000000011</v>
+      </c>
+      <c r="I17">
+        <v>109.2</v>
+      </c>
+      <c r="J17">
+        <v>77.100000000000009</v>
+      </c>
+      <c r="K17">
+        <v>95</v>
+      </c>
+      <c r="L17">
+        <v>99.2</v>
+      </c>
+      <c r="M17">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18">
+        <v>83.1</v>
+      </c>
+      <c r="D18">
+        <v>91.3</v>
+      </c>
+      <c r="E18">
+        <v>118.30000000000001</v>
+      </c>
+      <c r="F18">
+        <v>94.199999999999989</v>
+      </c>
+      <c r="G18">
+        <v>67.2</v>
+      </c>
+      <c r="H18">
+        <v>104.60000000000001</v>
+      </c>
+      <c r="I18">
+        <v>95</v>
+      </c>
+      <c r="J18">
+        <v>112.79999999999998</v>
+      </c>
+      <c r="K18">
+        <v>105.60000000000001</v>
+      </c>
+      <c r="M18">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
+        <v>94.699999999999989</v>
+      </c>
+      <c r="C19">
+        <v>105.89999999999999</v>
+      </c>
+      <c r="D19">
+        <v>85.5</v>
+      </c>
+      <c r="E19">
+        <v>92.600000000000009</v>
+      </c>
+      <c r="F19">
+        <v>96.2</v>
+      </c>
+      <c r="G19">
+        <v>85</v>
+      </c>
+      <c r="H19">
+        <v>71.8</v>
+      </c>
+      <c r="I19">
+        <v>99.3</v>
+      </c>
+      <c r="J19">
+        <v>68.7</v>
+      </c>
+      <c r="K19">
+        <v>93.7</v>
+      </c>
+      <c r="L19">
+        <v>100.69999999999999</v>
+      </c>
+      <c r="M19">
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
+        <v>86.4</v>
+      </c>
+      <c r="C20">
+        <v>105.2</v>
+      </c>
+      <c r="D20">
+        <v>101.4</v>
+      </c>
+      <c r="E20">
+        <v>103.89999999999999</v>
+      </c>
+      <c r="J20">
+        <v>104.1</v>
+      </c>
+      <c r="K20">
+        <v>109.80000000000001</v>
+      </c>
+      <c r="L20">
+        <v>103.2</v>
+      </c>
+      <c r="M20">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
+        <v>78.8</v>
+      </c>
+      <c r="C21">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="E21">
+        <v>98.9</v>
+      </c>
+      <c r="J21">
+        <v>99.2</v>
+      </c>
+      <c r="K21">
+        <v>99.2</v>
+      </c>
+      <c r="L21">
+        <v>98.5</v>
+      </c>
+      <c r="M21">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22">
+        <v>122</v>
+      </c>
+      <c r="C22">
+        <v>104.89999999999999</v>
+      </c>
+      <c r="D22">
+        <v>96.7</v>
+      </c>
+      <c r="E22">
+        <v>71.2</v>
+      </c>
+      <c r="J22">
+        <v>96.399999999999991</v>
+      </c>
+      <c r="K22">
+        <v>104.2</v>
+      </c>
+      <c r="L22">
+        <v>91.8</v>
+      </c>
+      <c r="M22">
+        <v>121.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23">
+        <v>96.6</v>
+      </c>
+      <c r="C23">
+        <v>94.199999999999989</v>
+      </c>
+      <c r="D23">
+        <v>105.4</v>
+      </c>
+      <c r="E23">
+        <v>99.6</v>
+      </c>
+      <c r="J23">
+        <v>86.4</v>
+      </c>
+      <c r="K23">
+        <v>83.1</v>
+      </c>
+      <c r="L23">
+        <v>106</v>
+      </c>
+      <c r="M23">
+        <v>102.89999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24">
+        <v>101</v>
+      </c>
+      <c r="C24">
+        <v>89.8</v>
+      </c>
+      <c r="D24">
+        <v>122.2</v>
+      </c>
+      <c r="E24">
+        <v>100.89999999999999</v>
+      </c>
+      <c r="J24">
+        <v>91.3</v>
+      </c>
+      <c r="L24">
+        <v>99.4</v>
+      </c>
+      <c r="M24">
+        <v>115.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25">
+        <v>78.600000000000009</v>
+      </c>
+      <c r="D25">
+        <v>92.2</v>
+      </c>
+      <c r="E25">
+        <v>136.9</v>
+      </c>
+      <c r="J25">
+        <v>92.7</v>
+      </c>
+      <c r="K25">
+        <v>128.19999999999999</v>
+      </c>
+      <c r="L25">
+        <v>109.1</v>
+      </c>
+      <c r="M25">
+        <v>95.399999999999991</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="C26">
+        <v>175.5</v>
+      </c>
+      <c r="D26">
+        <v>147.9</v>
+      </c>
+      <c r="E26">
+        <v>157.1</v>
+      </c>
+      <c r="F26">
+        <v>153.29999999999998</v>
+      </c>
+      <c r="G26">
+        <v>181.6</v>
+      </c>
+      <c r="H26">
+        <v>164.7</v>
+      </c>
+      <c r="I26">
+        <v>142.30000000000001</v>
+      </c>
+      <c r="J26">
+        <v>169.6</v>
+      </c>
+      <c r="K26">
+        <v>134.60000000000002</v>
+      </c>
+      <c r="L26">
+        <v>162.9</v>
+      </c>
+      <c r="M26">
+        <v>139.79999999999998</v>
+      </c>
+      <c r="N26">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="O26">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="P26">
+        <v>141.19999999999999</v>
+      </c>
+      <c r="Q26">
+        <v>156.29999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27">
+        <v>161.69999999999999</v>
+      </c>
+      <c r="C27">
+        <v>174</v>
+      </c>
+      <c r="D27">
+        <v>152.5</v>
+      </c>
+      <c r="E27">
+        <v>164.5</v>
+      </c>
+      <c r="G27">
+        <v>138.5</v>
+      </c>
+      <c r="H27">
+        <v>182.1</v>
+      </c>
+      <c r="I27">
+        <v>129.4</v>
+      </c>
+      <c r="J27">
+        <v>135.1</v>
+      </c>
+      <c r="K27">
+        <v>182.9</v>
+      </c>
+      <c r="L27">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="M27">
+        <v>146.19999999999999</v>
+      </c>
+      <c r="N27">
+        <v>149</v>
+      </c>
+      <c r="O27">
+        <v>183.7</v>
+      </c>
+      <c r="P27">
+        <v>181.7</v>
+      </c>
+      <c r="Q27">
+        <v>149.80000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28">
+        <v>142.70000000000002</v>
+      </c>
+      <c r="C28">
+        <v>147.4</v>
+      </c>
+      <c r="D28">
+        <v>173.70000000000002</v>
+      </c>
+      <c r="F28">
+        <v>163.19999999999999</v>
+      </c>
+      <c r="G28">
+        <v>177.4</v>
+      </c>
+      <c r="H28">
+        <v>172.9</v>
+      </c>
+      <c r="I28">
+        <v>156</v>
+      </c>
+      <c r="J28">
+        <v>159</v>
+      </c>
+      <c r="K28">
+        <v>157.6</v>
+      </c>
+      <c r="M28">
+        <v>144.9</v>
+      </c>
+      <c r="N28">
+        <v>159.5</v>
+      </c>
+      <c r="O28">
+        <v>158.6</v>
+      </c>
+      <c r="P28">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="Q28">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29">
+        <v>155.4</v>
+      </c>
+      <c r="D29">
+        <v>164.9</v>
+      </c>
+      <c r="E29">
+        <v>142.5</v>
+      </c>
+      <c r="F29">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="G29">
+        <v>160.20000000000002</v>
+      </c>
+      <c r="H29">
+        <v>157.6</v>
+      </c>
+      <c r="I29">
+        <v>170.79999999999998</v>
+      </c>
+      <c r="J29">
+        <v>141.79999999999998</v>
+      </c>
+      <c r="K29">
+        <v>153.6</v>
+      </c>
+      <c r="L29">
+        <v>134.5</v>
+      </c>
+      <c r="M29">
+        <v>148.5</v>
+      </c>
+      <c r="N29">
+        <v>154.20000000000002</v>
+      </c>
+      <c r="P29">
+        <v>143.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30">
+        <v>151</v>
+      </c>
+      <c r="C30">
+        <v>165</v>
+      </c>
+      <c r="D30">
+        <v>152.1</v>
+      </c>
+      <c r="E30">
+        <v>177.1</v>
+      </c>
+      <c r="F30">
+        <v>162.6</v>
+      </c>
+      <c r="G30">
+        <v>145.30000000000001</v>
+      </c>
+      <c r="H30">
+        <v>159.69999999999999</v>
+      </c>
+      <c r="J30">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="L30">
+        <v>175.4</v>
+      </c>
+      <c r="M30">
+        <v>159.5</v>
+      </c>
+      <c r="N30">
+        <v>164.3</v>
+      </c>
+      <c r="O30">
+        <v>139.6</v>
+      </c>
+      <c r="P30">
+        <v>137.1</v>
+      </c>
+      <c r="Q30">
+        <v>182.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31">
+        <v>155.6</v>
+      </c>
+      <c r="C31">
+        <v>174.6</v>
+      </c>
+      <c r="D31">
+        <v>167.70000000000002</v>
+      </c>
+      <c r="E31">
+        <v>171.3</v>
+      </c>
+      <c r="F31">
+        <v>170.70000000000002</v>
+      </c>
+      <c r="G31">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="H31">
+        <v>163.5</v>
+      </c>
+      <c r="I31">
+        <v>180.5</v>
+      </c>
+      <c r="J31">
+        <v>132.9</v>
+      </c>
+      <c r="K31">
+        <v>152.29999999999998</v>
+      </c>
+      <c r="L31">
+        <v>157.20000000000002</v>
+      </c>
+      <c r="M31">
+        <v>181.8</v>
+      </c>
+      <c r="N31">
+        <v>165</v>
+      </c>
+      <c r="O31">
+        <v>171.2</v>
+      </c>
+      <c r="P31">
+        <v>149.6</v>
+      </c>
+      <c r="Q31">
+        <v>173.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100168372A69B022D4B8DA341F10AFCD0C5" ma:contentTypeVersion="19" ma:contentTypeDescription="Crea un document nou" ma:contentTypeScope="" ma:versionID="969b68b5df23255ac8f50fc58ce49dd9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="467763d9-8723-4846-b585-067d7da271ed" xmlns:ns3="b5a02c93-71fc-48c6-941f-2c817c6654b2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="57b6b1cb209fe6b2b010d0a5fe1f4e51" ns2:_="" ns3:_="">
     <xsd:import namespace="467763d9-8723-4846-b585-067d7da271ed"/>
@@ -4596,15 +5929,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4617,6 +5941,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FCD0AB0-A0EC-49FE-B3FA-34D4C4B81DBF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499895CE-3781-457D-91AE-9F9D9BAA2A7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4635,14 +5967,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FCD0AB0-A0EC-49FE-B3FA-34D4C4B81DBF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4458C23-5E37-41CD-B9AD-18D4111980C3}">
   <ds:schemaRefs>
